--- a/data/trans_orig/P29A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P29A-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2007</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2007 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>251980</t>
+          <t>252350</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>295437</t>
+          <t>294161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103124</t>
+          <t>103591</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135940</t>
+          <t>138212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>364665</t>
+          <t>365088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>422317</t>
+          <t>421997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,02%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>167029</t>
+          <t>168305</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>210486</t>
+          <t>210116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>168524</t>
+          <t>166252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>201340</t>
+          <t>200873</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>344613</t>
+          <t>344933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>402265</t>
+          <t>401842</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195214</t>
+          <t>195728</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>234197</t>
+          <t>235061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121586</t>
+          <t>121746</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159286</t>
+          <t>157293</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327770</t>
+          <t>325780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>382418</t>
+          <t>382111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130143</t>
+          <t>129279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>169126</t>
+          <t>168612</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>208204</t>
+          <t>210197</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>245904</t>
+          <t>245744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349412</t>
+          <t>349719</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404060</t>
+          <t>406050</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>299548</t>
+          <t>298205</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>344219</t>
+          <t>341337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45488</t>
+          <t>44643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69868</t>
+          <t>68492</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>349504</t>
+          <t>350466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>405997</t>
+          <t>405206</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189799</t>
+          <t>192681</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>234470</t>
+          <t>235813</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97914</t>
+          <t>99290</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122294</t>
+          <t>123139</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295803</t>
+          <t>296594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>352296</t>
+          <t>351334</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>591498</t>
+          <t>592719</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>660863</t>
+          <t>660885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160713</t>
+          <t>161992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208965</t>
+          <t>207362</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>767316</t>
+          <t>763797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>854725</t>
+          <t>850942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>561745</t>
+          <t>561723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>631110</t>
+          <t>629889</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>501395</t>
+          <t>502998</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>549647</t>
+          <t>548368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1078243</t>
+          <t>1082026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1165652</t>
+          <t>1169171</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,49%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>185434</t>
+          <t>184260</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>222608</t>
+          <t>224069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109556</t>
+          <t>107414</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147809</t>
+          <t>148852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>301711</t>
+          <t>305053</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>362391</t>
+          <t>361430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125999</t>
+          <t>124538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163173</t>
+          <t>164347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>417604</t>
+          <t>416561</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>455857</t>
+          <t>457999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>551629</t>
+          <t>552590</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>612309</t>
+          <t>608967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116361</t>
+          <t>115555</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>150582</t>
+          <t>148078</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>172189</t>
+          <t>171848</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>222752</t>
+          <t>222039</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>296767</t>
+          <t>298954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>359515</t>
+          <t>361851</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143629</t>
+          <t>146133</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177850</t>
+          <t>178656</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1020944</t>
+          <t>1021657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1071507</t>
+          <t>1071848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1178392</t>
+          <t>1176056</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1241140</t>
+          <t>1238953</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1723564</t>
+          <t>1717544</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1830907</t>
+          <t>1831220</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>776980</t>
+          <t>771416</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>872060</t>
+          <t>873674</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2517316</t>
+          <t>2518645</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2683147</t>
+          <t>2678792</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1395343</t>
+          <t>1395030</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1502686</t>
+          <t>1508706</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2487146</t>
+          <t>2485532</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2582226</t>
+          <t>2587790</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3902309</t>
+          <t>3906664</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4068140</t>
+          <t>4066811</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2012</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2012 (tasa de respuesta: 96,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>246727</t>
+          <t>246179</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>289833</t>
+          <t>287896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112193</t>
+          <t>111249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>147927</t>
+          <t>148806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>367810</t>
+          <t>371317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>425957</t>
+          <t>424597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,47%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129141</t>
+          <t>131078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172247</t>
+          <t>172795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159289</t>
+          <t>158410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>195023</t>
+          <t>195967</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>300233</t>
+          <t>301593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>358380</t>
+          <t>354873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>48,87%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>213764</t>
+          <t>213066</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>253550</t>
+          <t>254573</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103893</t>
+          <t>104083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>141566</t>
+          <t>138939</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>329461</t>
+          <t>326544</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>385214</t>
+          <t>385686</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>149062</t>
+          <t>148039</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188848</t>
+          <t>189546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>185575</t>
+          <t>188202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>223248</t>
+          <t>223058</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344539</t>
+          <t>344067</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>400292</t>
+          <t>403209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>316312</t>
+          <t>315429</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>365662</t>
+          <t>366750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50622</t>
+          <t>50489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78189</t>
+          <t>78115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>372568</t>
+          <t>376162</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>433011</t>
+          <t>437254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,84%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>226853</t>
+          <t>225765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276203</t>
+          <t>277086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172708</t>
+          <t>172782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200275</t>
+          <t>200408</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>410401</t>
+          <t>406158</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>470844</t>
+          <t>467250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>550298</t>
+          <t>551558</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>617659</t>
+          <t>619738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>171366</t>
+          <t>169265</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220104</t>
+          <t>218208</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>732704</t>
+          <t>735864</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>821081</t>
+          <t>820703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486651</t>
+          <t>484572</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>554012</t>
+          <t>552752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>526263</t>
+          <t>528159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>575001</t>
+          <t>577102</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1029596</t>
+          <t>1029974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1117973</t>
+          <t>1114813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>257114</t>
+          <t>254020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>299555</t>
+          <t>299325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134797</t>
+          <t>134606</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182262</t>
+          <t>180603</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>401545</t>
+          <t>395868</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>470003</t>
+          <t>466406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189038</t>
+          <t>189268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>231479</t>
+          <t>234573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>570861</t>
+          <t>572520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>618326</t>
+          <t>618517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>771713</t>
+          <t>775310</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>840171</t>
+          <t>845848</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,12%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116337</t>
+          <t>115212</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147740</t>
+          <t>146082</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>202171</t>
+          <t>199889</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>259122</t>
+          <t>256247</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>327743</t>
+          <t>325396</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>393063</t>
+          <t>390395</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>114963</t>
+          <t>116621</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146366</t>
+          <t>147491</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>835115</t>
+          <t>837990</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>892066</t>
+          <t>894348</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>963877</t>
+          <t>966545</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1029197</t>
+          <t>1031544</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,02%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1778848</t>
+          <t>1779659</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1894663</t>
+          <t>1889648</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>844897</t>
+          <t>840032</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>950267</t>
+          <t>945286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2651416</t>
+          <t>2658260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2815308</t>
+          <t>2817710</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,75%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1375044</t>
+          <t>1380059</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1490859</t>
+          <t>1490048</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2528714</t>
+          <t>2533695</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2634084</t>
+          <t>2638949</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3933380</t>
+          <t>3930978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4097272</t>
+          <t>4090428</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,61%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2016</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2016 (tasa de respuesta: 97,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>256277</t>
+          <t>254676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>296065</t>
+          <t>294701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>125182</t>
+          <t>124707</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>161560</t>
+          <t>162036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>393424</t>
+          <t>389426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>450113</t>
+          <t>447975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121747</t>
+          <t>123111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161535</t>
+          <t>163136</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172528</t>
+          <t>172052</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>208906</t>
+          <t>209381</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>301788</t>
+          <t>303926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>358477</t>
+          <t>362475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>209801</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>248980</t>
+          <t>247595</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>157339</t>
+          <t>157106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>198070</t>
+          <t>199140</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>379376</t>
+          <t>377748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>434446</t>
+          <t>434701</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,54%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118499</t>
+          <t>119884</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158823</t>
+          <t>157678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164520</t>
+          <t>163450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>205251</t>
+          <t>205484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295623</t>
+          <t>295368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>350693</t>
+          <t>352321</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>289962</t>
+          <t>290847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>333904</t>
+          <t>334692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39504</t>
+          <t>39773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63768</t>
+          <t>65011</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>338650</t>
+          <t>339385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>390751</t>
+          <t>389267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>169238</t>
+          <t>168450</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>213180</t>
+          <t>212295</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98314</t>
+          <t>97071</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122578</t>
+          <t>122309</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>274473</t>
+          <t>275957</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326574</t>
+          <t>325839</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,98%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>580087</t>
+          <t>577191</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>646949</t>
+          <t>648873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252004</t>
+          <t>254834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>304882</t>
+          <t>309014</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>847356</t>
+          <t>843867</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>943765</t>
+          <t>936229</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>463651</t>
+          <t>461727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>530513</t>
+          <t>533409</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>512751</t>
+          <t>508619</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>565629</t>
+          <t>562799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>984468</t>
+          <t>992004</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1080877</t>
+          <t>1084366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>267445</t>
+          <t>269690</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>317692</t>
+          <t>319663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>147334</t>
+          <t>149236</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>195656</t>
+          <t>196653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>432884</t>
+          <t>432833</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>506108</t>
+          <t>501811</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>282812</t>
+          <t>280841</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333059</t>
+          <t>330814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>532376</t>
+          <t>531379</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>580698</t>
+          <t>578796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>822428</t>
+          <t>826725</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>895652</t>
+          <t>895703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>130885</t>
+          <t>132415</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>166285</t>
+          <t>167102</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>215597</t>
+          <t>212924</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>270493</t>
+          <t>268832</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>359210</t>
+          <t>354881</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>425029</t>
+          <t>426801</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>113200</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149417</t>
+          <t>147887</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>800199</t>
+          <t>801860</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>855095</t>
+          <t>857768</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>925964</t>
+          <t>924192</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>991783</t>
+          <t>996112</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1810969</t>
+          <t>1819834</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1926934</t>
+          <t>1934005</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1009775</t>
+          <t>1010951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1122062</t>
+          <t>1120415</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2860487</t>
+          <t>2859140</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3031962</t>
+          <t>3022411</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1352904</t>
+          <t>1345833</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1468869</t>
+          <t>1460004</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2353056</t>
+          <t>2354703</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2465343</t>
+          <t>2464167</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3722994</t>
+          <t>3732545</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3894469</t>
+          <t>3895816</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,67%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2023</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>260248</t>
+          <t>258925</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>306152</t>
+          <t>306776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144281</t>
+          <t>144924</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>178939</t>
+          <t>180045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>417969</t>
+          <t>416159</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>476458</t>
+          <t>478093</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,18%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199060</t>
+          <t>198436</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244964</t>
+          <t>246287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268528</t>
+          <t>267422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303186</t>
+          <t>302543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>476221</t>
+          <t>474586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>534710</t>
+          <t>536520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>190511</t>
+          <t>192207</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>233748</t>
+          <t>234416</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118422</t>
+          <t>119031</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150074</t>
+          <t>150193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>321926</t>
+          <t>318602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>377193</t>
+          <t>373562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>218465</t>
+          <t>217797</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>261702</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231190</t>
+          <t>231071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>262842</t>
+          <t>262233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>456284</t>
+          <t>459915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>511551</t>
+          <t>514875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,77%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82989</t>
+          <t>81719</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>341003</t>
+          <t>345020</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32292</t>
+          <t>31971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49523</t>
+          <t>50974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106439</t>
+          <t>129203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>366325</t>
+          <t>366174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,91%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>326850</t>
+          <t>322833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>584864</t>
+          <t>586134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116601</t>
+          <t>115150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133832</t>
+          <t>134153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>467652</t>
+          <t>467803</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>727538</t>
+          <t>704774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>472952</t>
+          <t>475159</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>547191</t>
+          <t>543838</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>257414</t>
+          <t>256659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>658884</t>
+          <t>694449</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>785700</t>
+          <t>788921</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1233061</t>
+          <t>1243566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>483231</t>
+          <t>486584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>557470</t>
+          <t>555263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>317639</t>
+          <t>282074</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>719109</t>
+          <t>719864</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>773884</t>
+          <t>763379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1221245</t>
+          <t>1218024</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,69%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>209005</t>
+          <t>209111</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>254329</t>
+          <t>255793</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>97644</t>
+          <t>95105</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>156451</t>
+          <t>152495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>292210</t>
+          <t>293663</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>403020</t>
+          <t>404049</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>218920</t>
+          <t>217456</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264244</t>
+          <t>264138</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>680745</t>
+          <t>684701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>739552</t>
+          <t>742091</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>907425</t>
+          <t>906396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1018235</t>
+          <t>1016782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,59%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70457</t>
+          <t>69601</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124546</t>
+          <t>123566</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>101513</t>
+          <t>102433</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145585</t>
+          <t>144453</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>184813</t>
+          <t>185609</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>258981</t>
+          <t>255062</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115961</t>
+          <t>116941</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>170050</t>
+          <t>170906</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>613951</t>
+          <t>615083</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>658023</t>
+          <t>657103</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>741062</t>
+          <t>744981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>815230</t>
+          <t>814434</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1213972</t>
+          <t>1137048</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1688376</t>
+          <t>1683124</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>832219</t>
+          <t>828328</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1522179</t>
+          <t>1542095</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2296421</t>
+          <t>2313769</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2957516</t>
+          <t>2924351</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -10804,17 +10804,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1825238</t>
+          <t>1825239</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1681080</t>
+          <t>1686333</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2155484</t>
+          <t>2232409</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2045930</t>
+          <t>2026014</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2735890</t>
+          <t>2739781</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3980050</t>
+          <t>4013215</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4641145</t>
+          <t>4623797</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,65%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3369456</t>
+          <t>3369457</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3369456</t>
+          <t>3369457</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3369456</t>
+          <t>3369457</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">

--- a/data/trans_orig/P29A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P29A-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>252350</t>
+          <t>251005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>294161</t>
+          <t>296415</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103591</t>
+          <t>101744</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138212</t>
+          <t>136866</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>365088</t>
+          <t>363887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>421997</t>
+          <t>423555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>168305</t>
+          <t>166051</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>210116</t>
+          <t>211461</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166252</t>
+          <t>167598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>200873</t>
+          <t>202720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>344933</t>
+          <t>343375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>401842</t>
+          <t>403043</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195728</t>
+          <t>194551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>235061</t>
+          <t>234576</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121746</t>
+          <t>121209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157293</t>
+          <t>160835</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>325780</t>
+          <t>329058</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>382111</t>
+          <t>383837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129279</t>
+          <t>129764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>168612</t>
+          <t>169789</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210197</t>
+          <t>206655</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>245744</t>
+          <t>246281</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349719</t>
+          <t>347993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>406050</t>
+          <t>402772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,04%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>298205</t>
+          <t>296627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>341337</t>
+          <t>344710</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44643</t>
+          <t>44522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68492</t>
+          <t>68793</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>350466</t>
+          <t>351421</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>405206</t>
+          <t>403197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>192681</t>
+          <t>189308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>235813</t>
+          <t>237391</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99290</t>
+          <t>98989</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123139</t>
+          <t>123260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>296594</t>
+          <t>298603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>351334</t>
+          <t>350379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>592719</t>
+          <t>589878</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>660885</t>
+          <t>661603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>161992</t>
+          <t>159732</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207362</t>
+          <t>207157</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>763797</t>
+          <t>765013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>850942</t>
+          <t>849279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>561723</t>
+          <t>561005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>629889</t>
+          <t>632730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>502998</t>
+          <t>503203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>548368</t>
+          <t>550628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1082026</t>
+          <t>1083689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1169171</t>
+          <t>1167955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>184260</t>
+          <t>184233</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>224069</t>
+          <t>223131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107414</t>
+          <t>107965</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148852</t>
+          <t>149415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>305053</t>
+          <t>300285</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>361430</t>
+          <t>359102</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124538</t>
+          <t>125476</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164347</t>
+          <t>164374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>416561</t>
+          <t>415998</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>457999</t>
+          <t>457448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>552590</t>
+          <t>554918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>608967</t>
+          <t>613735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>115555</t>
+          <t>115303</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>148078</t>
+          <t>148821</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>171848</t>
+          <t>173781</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>222039</t>
+          <t>224680</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>298954</t>
+          <t>299768</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>361851</t>
+          <t>360175</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146133</t>
+          <t>145390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178656</t>
+          <t>178908</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1021657</t>
+          <t>1019016</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1071848</t>
+          <t>1069915</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1176056</t>
+          <t>1177732</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1238953</t>
+          <t>1238139</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,51%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1717544</t>
+          <t>1717242</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1831220</t>
+          <t>1830525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>771416</t>
+          <t>773782</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>873674</t>
+          <t>871409</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2518645</t>
+          <t>2516018</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2678792</t>
+          <t>2676494</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1395030</t>
+          <t>1395725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1508706</t>
+          <t>1509008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2485532</t>
+          <t>2487797</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2587790</t>
+          <t>2585424</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3906664</t>
+          <t>3908962</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4066811</t>
+          <t>4069438</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,79%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>246179</t>
+          <t>245523</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>287896</t>
+          <t>288575</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111249</t>
+          <t>112948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148806</t>
+          <t>150033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>371317</t>
+          <t>371443</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>424597</t>
+          <t>426227</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,69%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131078</t>
+          <t>130399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172795</t>
+          <t>173451</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158410</t>
+          <t>157183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>195967</t>
+          <t>194268</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>301593</t>
+          <t>299963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>354873</t>
+          <t>354747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,85%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>213066</t>
+          <t>213598</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>254573</t>
+          <t>257846</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104083</t>
+          <t>104887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138939</t>
+          <t>141499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>326544</t>
+          <t>329623</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>385686</t>
+          <t>386369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148039</t>
+          <t>144766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>189546</t>
+          <t>189014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188202</t>
+          <t>185642</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>223058</t>
+          <t>222254</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344067</t>
+          <t>343384</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>403209</t>
+          <t>400130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,83%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>315429</t>
+          <t>313108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>366750</t>
+          <t>364855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50489</t>
+          <t>51471</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78115</t>
+          <t>78957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>376162</t>
+          <t>375169</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>437254</t>
+          <t>434750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>225765</t>
+          <t>227660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277086</t>
+          <t>279407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172782</t>
+          <t>171940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200408</t>
+          <t>199426</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>406158</t>
+          <t>408662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>467250</t>
+          <t>468243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,52%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>551558</t>
+          <t>546901</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>619738</t>
+          <t>616351</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169265</t>
+          <t>169877</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>218208</t>
+          <t>219995</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>735864</t>
+          <t>733606</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>820703</t>
+          <t>819795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,3%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>484572</t>
+          <t>487959</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>552752</t>
+          <t>557409</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>528159</t>
+          <t>526372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>577102</t>
+          <t>576490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1029974</t>
+          <t>1030882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1114813</t>
+          <t>1117071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,36%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>254020</t>
+          <t>256794</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>299325</t>
+          <t>299243</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134606</t>
+          <t>133150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>180603</t>
+          <t>180349</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>395868</t>
+          <t>401937</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>466406</t>
+          <t>467438</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189268</t>
+          <t>189350</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>234573</t>
+          <t>231799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>572520</t>
+          <t>572774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>618517</t>
+          <t>619973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>775310</t>
+          <t>774278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>845848</t>
+          <t>839779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,63%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>115212</t>
+          <t>115209</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>146082</t>
+          <t>147540</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>199889</t>
+          <t>202831</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>256247</t>
+          <t>257735</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>325396</t>
+          <t>323457</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>390395</t>
+          <t>394788</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116621</t>
+          <t>115163</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>147491</t>
+          <t>147494</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>837990</t>
+          <t>836502</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>894348</t>
+          <t>891406</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>966545</t>
+          <t>962152</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1031544</t>
+          <t>1033483</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1779659</t>
+          <t>1785304</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1889648</t>
+          <t>1898607</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>840032</t>
+          <t>846058</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>945286</t>
+          <t>947581</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2658260</t>
+          <t>2645647</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2817710</t>
+          <t>2817141</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1380059</t>
+          <t>1371100</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1490048</t>
+          <t>1484403</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2533695</t>
+          <t>2531400</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2638949</t>
+          <t>2632923</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3930978</t>
+          <t>3931547</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4090428</t>
+          <t>4103041</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>254676</t>
+          <t>256796</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>294701</t>
+          <t>295449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124707</t>
+          <t>124841</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>162036</t>
+          <t>162491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>389426</t>
+          <t>391757</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>447975</t>
+          <t>447458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,51%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123111</t>
+          <t>122363</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163136</t>
+          <t>161016</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172052</t>
+          <t>171597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>209381</t>
+          <t>209247</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>303926</t>
+          <t>304443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>362475</t>
+          <t>360144</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,9%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>209801</t>
+          <t>208474</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>247595</t>
+          <t>246071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>157106</t>
+          <t>159399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>199140</t>
+          <t>197854</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>377748</t>
+          <t>378721</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>434701</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119884</t>
+          <t>121408</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157678</t>
+          <t>159005</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>163450</t>
+          <t>164736</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>205484</t>
+          <t>203191</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295368</t>
+          <t>298013</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>352321</t>
+          <t>351348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,13%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>290847</t>
+          <t>289475</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>334692</t>
+          <t>333685</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39773</t>
+          <t>39110</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65011</t>
+          <t>64633</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>339385</t>
+          <t>339495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>389267</t>
+          <t>391665</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,88%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168450</t>
+          <t>169457</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>212295</t>
+          <t>213667</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97071</t>
+          <t>97449</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122309</t>
+          <t>122972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275957</t>
+          <t>273559</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325839</t>
+          <t>325729</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>577191</t>
+          <t>579929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>648873</t>
+          <t>647819</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>254834</t>
+          <t>254477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>309014</t>
+          <t>309463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>843867</t>
+          <t>845535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>936229</t>
+          <t>936607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,57%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>461727</t>
+          <t>462781</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>533409</t>
+          <t>530671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>508619</t>
+          <t>508170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>562799</t>
+          <t>563156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>992004</t>
+          <t>991626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1084366</t>
+          <t>1082698</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,15%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>269690</t>
+          <t>269121</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>319663</t>
+          <t>318907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149236</t>
+          <t>149788</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>196653</t>
+          <t>196711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>432833</t>
+          <t>430499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>501811</t>
+          <t>501735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>280841</t>
+          <t>281597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>330814</t>
+          <t>331383</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>531379</t>
+          <t>531321</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>578796</t>
+          <t>578244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>826725</t>
+          <t>826801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>895703</t>
+          <t>898037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,6%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>132415</t>
+          <t>131877</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>167102</t>
+          <t>165186</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>212924</t>
+          <t>212582</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>268832</t>
+          <t>270136</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>354881</t>
+          <t>355376</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>426801</t>
+          <t>425516</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113200</t>
+          <t>115116</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>147887</t>
+          <t>148425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>801860</t>
+          <t>800556</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>857768</t>
+          <t>858110</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>924192</t>
+          <t>925477</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>996112</t>
+          <t>995617</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,7%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1819834</t>
+          <t>1813523</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1934005</t>
+          <t>1928264</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1010951</t>
+          <t>1017638</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1120415</t>
+          <t>1120748</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2859140</t>
+          <t>2862517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3022411</t>
+          <t>3036891</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1345833</t>
+          <t>1351574</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1460004</t>
+          <t>1466315</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2354703</t>
+          <t>2354370</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2464167</t>
+          <t>2457480</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3732545</t>
+          <t>3718065</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3895816</t>
+          <t>3892439</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>283735</t>
+          <t>304682</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>258925</t>
+          <t>278202</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>306776</t>
+          <t>330597</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144924</t>
+          <t>155958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>180045</t>
+          <t>192111</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>446479</t>
+          <t>480096</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>416159</t>
+          <t>449990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>478093</t>
+          <t>511361</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>49,22%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>221477</t>
+          <t>245936</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198436</t>
+          <t>220021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246287</t>
+          <t>272416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>284723</t>
+          <t>312997</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267422</t>
+          <t>296300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302543</t>
+          <t>332453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>506200</t>
+          <t>558933</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>474586</t>
+          <t>527668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>536520</t>
+          <t>589039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>212965</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>192207</t>
+          <t>200751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>234416</t>
+          <t>247876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>133901</t>
+          <t>145667</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119031</t>
+          <t>130381</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150193</t>
+          <t>163384</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>346866</t>
+          <t>370358</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>318602</t>
+          <t>344601</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>373562</t>
+          <t>397495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>239248</t>
+          <t>258521</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>217797</t>
+          <t>235336</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>260006</t>
+          <t>282461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>247363</t>
+          <t>276020</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231071</t>
+          <t>258303</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>262233</t>
+          <t>291306</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>486611</t>
+          <t>534541</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>459915</t>
+          <t>507404</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>514875</t>
+          <t>560298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381264</t>
+          <t>421687</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381264</t>
+          <t>421687</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381264</t>
+          <t>421687</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833477</t>
+          <t>904899</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833477</t>
+          <t>904899</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833477</t>
+          <t>904899</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>210884</t>
+          <t>227684</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81719</t>
+          <t>204768</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>345020</t>
+          <t>248332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31971</t>
+          <t>36818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50974</t>
+          <t>56601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>251217</t>
+          <t>274249</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129203</t>
+          <t>249734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>366174</t>
+          <t>298302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>456969</t>
+          <t>243503</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322833</t>
+          <t>222855</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>586134</t>
+          <t>266419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125791</t>
+          <t>139902</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115150</t>
+          <t>129866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134153</t>
+          <t>149649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>582760</t>
+          <t>383406</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>467803</t>
+          <t>359353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>704774</t>
+          <t>407921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>62,03%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667853</t>
+          <t>471187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667853</t>
+          <t>471187</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667853</t>
+          <t>471187</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166124</t>
+          <t>186467</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166124</t>
+          <t>186467</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166124</t>
+          <t>186467</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>833977</t>
+          <t>657655</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833977</t>
+          <t>657655</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>833977</t>
+          <t>657655</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>509939</t>
+          <t>544072</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>475159</t>
+          <t>506643</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>543838</t>
+          <t>578834</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>414766</t>
+          <t>230439</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>256659</t>
+          <t>207734</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>694449</t>
+          <t>255824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>924705</t>
+          <t>774512</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>788921</t>
+          <t>729841</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1243566</t>
+          <t>818026</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>41,17%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>520483</t>
+          <t>583231</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486584</t>
+          <t>548469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>555263</t>
+          <t>620660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>561757</t>
+          <t>629090</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282074</t>
+          <t>603705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>719864</t>
+          <t>651795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1082240</t>
+          <t>1212321</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>763379</t>
+          <t>1168807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1218024</t>
+          <t>1256992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>63,27%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1030422</t>
+          <t>1127303</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1030422</t>
+          <t>1127303</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1030422</t>
+          <t>1127303</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>976523</t>
+          <t>859529</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>976523</t>
+          <t>859529</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>976523</t>
+          <t>859529</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2006945</t>
+          <t>1986833</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2006945</t>
+          <t>1986833</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2006945</t>
+          <t>1986833</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>231835</t>
+          <t>257777</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>209111</t>
+          <t>231079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>255793</t>
+          <t>284084</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>130663</t>
+          <t>152817</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95105</t>
+          <t>133682</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>152495</t>
+          <t>174600</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>362498</t>
+          <t>410594</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>293663</t>
+          <t>376635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>404049</t>
+          <t>447201</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>241414</t>
+          <t>308351</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>217456</t>
+          <t>282044</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264138</t>
+          <t>335049</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>706533</t>
+          <t>675424</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>684701</t>
+          <t>653641</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>742091</t>
+          <t>694559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>947947</t>
+          <t>983775</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>906396</t>
+          <t>947168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1016782</t>
+          <t>1017734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>72,99%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473249</t>
+          <t>566128</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473249</t>
+          <t>566128</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473249</t>
+          <t>566128</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837196</t>
+          <t>828241</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837196</t>
+          <t>828241</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>837196</t>
+          <t>828241</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1310445</t>
+          <t>1394369</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1310445</t>
+          <t>1394369</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1310445</t>
+          <t>1394369</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69601</t>
+          <t>65829</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123566</t>
+          <t>111258</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>122080</t>
+          <t>127207</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102433</t>
+          <t>108037</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>144453</t>
+          <t>151009</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>216940</t>
+          <t>213048</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>185609</t>
+          <t>183502</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>255062</t>
+          <t>249044</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>145647</t>
+          <t>151387</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116941</t>
+          <t>125970</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>170906</t>
+          <t>171399</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>637456</t>
+          <t>715048</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>615083</t>
+          <t>691246</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>657103</t>
+          <t>734218</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>783103</t>
+          <t>866434</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>744981</t>
+          <t>830438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>814434</t>
+          <t>895980</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759536</t>
+          <t>842255</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759536</t>
+          <t>842255</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759536</t>
+          <t>842255</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000043</t>
+          <t>1079482</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000043</t>
+          <t>1079482</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000043</t>
+          <t>1079482</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1544218</t>
+          <t>1644749</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1137048</t>
+          <t>1580921</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1683124</t>
+          <t>1708454</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1004487</t>
+          <t>878109</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>828328</t>
+          <t>828959</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1542095</t>
+          <t>918711</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2548705</t>
+          <t>2522857</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2313769</t>
+          <t>2433601</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2924351</t>
+          <t>2602207</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1825239</t>
+          <t>1790928</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1686333</t>
+          <t>1727223</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2232409</t>
+          <t>1854756</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2563622</t>
+          <t>2748481</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026014</t>
+          <t>2707879</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2739781</t>
+          <t>2797631</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4388861</t>
+          <t>4539410</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4013215</t>
+          <t>4460060</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4623797</t>
+          <t>4628666</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>65,54%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3369457</t>
+          <t>3435677</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3369457</t>
+          <t>3435677</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3369457</t>
+          <t>3435677</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3568109</t>
+          <t>3626590</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3568109</t>
+          <t>3626590</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3568109</t>
+          <t>3626590</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6937566</t>
+          <t>7062267</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6937566</t>
+          <t>7062267</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6937566</t>
+          <t>7062267</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
